--- a/vinyl-label-printer/data/database.xlsx
+++ b/vinyl-label-printer/data/database.xlsx
@@ -1,88 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Nextcloud\Coding\vinylsticker\vinyl-label-printer\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3438B3-A6AF-4D4D-9FA3-CA913B5ADAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Print" sheetId="1" r:id="rId1"/>
-    <sheet name="Database" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Print" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Artist</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Side</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Test-Label</t>
-  </si>
-  <si>
-    <t>Test-Title B</t>
-  </si>
-  <si>
-    <t>Test-Artist</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -101,22 +55,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -295,121 +308,363 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col width="24.28515625" customWidth="1" min="1" max="1"/>
+    <col width="22.7109375" customWidth="1" min="2" max="2"/>
+    <col width="19.7109375" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10.85546875" customWidth="1" min="5" max="5"/>
+    <col width="4.85546875" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Billy-Goat</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The Maytones</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Blue Cat Records BS 149</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Call You Up</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The Maytones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Blue Cat Records BS 149</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kill Me Dead</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Derrick Morgan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pyramid (2) PYR 6021</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Don't Be A Fool</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Derrick Morgan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pyramid (2) PYR 6021</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Drink Milk</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Justin Hinds</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Treasure Isle</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Travel With Love</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Justin Hinds</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Treasure Isle</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col width="25.85546875" customWidth="1" min="1" max="1"/>
+    <col width="22.7109375" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4.85546875" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Test-Title B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test-Artist</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Test-Label</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>2014</v>
       </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Test-Title B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Test-Artist</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Test-Label</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>2014</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>